--- a/results_(stress_test)_PCCxSigmoid-PLI-/summary_PCC_PLI_20250413.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/summary_PCC_PLI_20250413.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64A6863-67AF-4215-BD71-9B3F9EB8CD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9518283-9AAF-4904-9A14-23B8AC7D6220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nm_basis_F, nm_modifier_F" sheetId="8" r:id="rId1"/>
@@ -547,45 +547,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -940,38 +940,38 @@
       <c r="V1" s="72"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="79"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="84"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="72"/>
-      <c r="M2" s="77" t="s">
+      <c r="M2" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="79"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="84"/>
       <c r="V2" s="72"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="15">
         <v>93.101364775358491</v>
       </c>
@@ -1005,10 +1005,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M3" s="77" t="s">
+      <c r="M3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="79"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="15">
         <v>3.4649270444699574</v>
       </c>
@@ -1036,10 +1036,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="22">
         <v>87.593900000000005</v>
       </c>
@@ -1070,13 +1070,13 @@
         <v>81.468931946607086</v>
       </c>
       <c r="L4" s="72" t="str">
-        <f t="shared" ref="L4:L10" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="77" t="s">
+      <c r="M4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="79"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="51">
         <v>2.4529187882918819</v>
       </c>
@@ -1099,36 +1099,36 @@
         <v>3.7419646549723868</v>
       </c>
       <c r="V4" s="72" t="str">
-        <f t="shared" ref="V4:V10" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O4:U4)&amp;","</f>
+        <f t="shared" ref="V4:V10" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O4:U4)&amp;","</f>
         <v xml:space="preserve">    2.45291878829188, 2.16276566139488, 2.29733988047472, 2.13416531965459, 2.38348787528267, 3.78798604641006, 3.74196465497239,</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="84"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="72"/>
-      <c r="M5" s="77" t="s">
+      <c r="M5" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="79"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="87"/>
+      <c r="U5" s="84"/>
       <c r="V5" s="72"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>83.335515950253324</v>
       </c>
       <c r="L6" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:I6)&amp;","</f>
         <v xml:space="preserve">    93.2999016715831, 92.0973566668685, 91.0540863963645, 88.6610726159684, 85.7395652211524, 68.3374106465742, 46.5238568961093,</v>
       </c>
       <c r="M6" s="21" t="s">
@@ -1199,7 +1199,7 @@
         <v>5.301203589536982</v>
       </c>
       <c r="V6" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.34703402839045, 3.88104213198084, 3.49567070632551, 3.15121946781627, 3.37813490354902, 6.62669565247047, 5.30120358953698,</v>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
         <v>83.577137922185017</v>
       </c>
       <c r="L7" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:I7)&amp;","</f>
         <v xml:space="preserve">    93.0383538496584, 92.0973451327434, 91.2074844938105, 88.5044363128862, 86.3718428936813, 70.6380879880737, 47.6246824511169,</v>
       </c>
       <c r="M7" s="21" t="s">
@@ -1271,7 +1271,7 @@
         <v>4.0794731079556916</v>
       </c>
       <c r="V7" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.59168456500624, 3.63154160517083, 3.47474439934664, 3.05077599198478, 3.40859273965194, 5.85801581439331, 4.07947310795569,</v>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>83.821168075271714</v>
       </c>
       <c r="L8" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C8:I8)&amp;","</f>
         <v xml:space="preserve">    92.7423795476893, 92.2173115684392, 91.2812250394323, 89.0289362364726, 86.5807143660412, 72.2072480442449, 48.3124652174038,</v>
       </c>
       <c r="M8" s="21" t="s">
@@ -1343,7 +1343,7 @@
         <v>4.9343093065934669</v>
       </c>
       <c r="V8" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.55772662916483, 3.59803300735117, 3.21137352330287, 3.00646636749615, 3.12666441939204, 4.68368718707673, 4.93430930659347,</v>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         <v>84.448559459856938</v>
       </c>
       <c r="L9" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    92.9174041297935, 92.7463126843658, 91.5398230088496, 89.5516800895048, 87.7630198646471, 74.8149839819837, 49.2267118804373,</v>
       </c>
       <c r="M9" s="21" t="s">
@@ -1415,7 +1415,7 @@
         <v>5.8657035603227596</v>
       </c>
       <c r="V9" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.26029526424707, 3.28906438079358, 2.95004325833602, 2.96629740711421, 2.95812542676641, 5.49623606192297, 5.86570356032276,</v>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
         <v>84.382587868407157</v>
       </c>
       <c r="L10" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:I10)&amp;","</f>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
       <c r="M10" s="4" t="s">
@@ -1487,43 +1487,43 @@
         <v>5.9316401890770027</v>
       </c>
       <c r="V10" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.14920929515277, 3.31820763369914, 3.19816618617616, 3.13212695988859, 3.07506319977273, 5.16611420499541, 5.931640189077,</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="81"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="86"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="72"/>
-      <c r="M11" s="77" t="s">
+      <c r="M11" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="78"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="80"/>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80"/>
-      <c r="U11" s="81"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="86"/>
       <c r="V11" s="72"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -1554,13 +1554,13 @@
         <v>81.635477022580943</v>
       </c>
       <c r="L12" s="72" t="str">
-        <f t="shared" ref="L12:L15" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M12" s="77" t="s">
+      <c r="M12" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="N12" s="79"/>
+      <c r="N12" s="84"/>
       <c r="O12" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -1583,15 +1583,15 @@
         <v>5.203571843512913</v>
       </c>
       <c r="V12" s="72" t="str">
-        <f t="shared" ref="V12:V15" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O12:U12)&amp;","</f>
+        <f t="shared" ref="V12:V15" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O12:U12)&amp;","</f>
         <v xml:space="preserve">    3.39919218235549, 3.656148978379, 3.43161793888068, 3.36107812276178, 5.27738358730928, 8.20271301965104, 5.20357184351291,</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="81"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -1622,13 +1622,13 @@
         <v>82.625440098962798</v>
       </c>
       <c r="L13" s="72" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C13:I13)&amp;","</f>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M13" s="77" t="s">
+      <c r="M13" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="79"/>
+      <c r="N13" s="84"/>
       <c r="O13" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -1651,15 +1651,15 @@
         <v>2.488810891584841</v>
       </c>
       <c r="V13" s="72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.19031227155556, 2.88280360646228, 2.58847407711463, 2.62134504708773, 3.20356998968766, 4.75671211275067, 2.48881089158484,</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="79"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -1690,13 +1690,13 @@
         <v>81.55872152873296</v>
       </c>
       <c r="L14" s="72" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M14" s="77" t="s">
+      <c r="M14" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="N14" s="79"/>
+      <c r="N14" s="84"/>
       <c r="O14" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -1719,15 +1719,15 @@
         <v>9.2355901481835172</v>
       </c>
       <c r="V14" s="72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.72078192123604, 4.04671527762167, 4.023576362777, 4.47676332123312, 7.20190165275039, 10.0466843686008, 9.23559014818352,</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="79"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="58">
         <v>93.174110502686005</v>
       </c>
@@ -1758,13 +1758,13 @@
         <v>80.686930106085114</v>
       </c>
       <c r="L15" s="72" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:I15)&amp;","</f>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M15" s="77" t="s">
+      <c r="M15" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="N15" s="79"/>
+      <c r="N15" s="84"/>
       <c r="O15" s="58">
         <v>3.8766021792735019</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>9.200486032966916</v>
       </c>
       <c r="V15" s="72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.8766021792735, 4.81264114062281, 4.6512210016048, 5.24160663557633, 8.07695886022353, 10.6573633075615, 9.20048603296692,</v>
       </c>
     </row>
@@ -1876,38 +1876,38 @@
       <c r="V17" s="74"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="84"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="85"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="78"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="74"/>
-      <c r="M18" s="83" t="s">
+      <c r="M18" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="84"/>
-      <c r="O18" s="84"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="85"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="79"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="78"/>
       <c r="V18" s="74"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="85"/>
+      <c r="B19" s="78"/>
       <c r="C19" s="25">
         <v>92.567111769713335</v>
       </c>
@@ -1935,10 +1935,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M19" s="83" t="s">
+      <c r="M19" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="N19" s="85"/>
+      <c r="N19" s="78"/>
       <c r="O19" s="27">
         <v>3.88093621561358</v>
       </c>
@@ -1966,10 +1966,10 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="85"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="25">
         <v>92.866950218042462</v>
       </c>
@@ -1997,10 +1997,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M20" s="83" t="s">
+      <c r="M20" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="N20" s="85"/>
+      <c r="N20" s="78"/>
       <c r="O20" s="25">
         <v>3.8319643020864191</v>
       </c>
@@ -2023,15 +2023,15 @@
         <v>10.021578856839133</v>
       </c>
       <c r="V20" s="74" t="str">
-        <f t="shared" ref="V20:V32" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O20:U20)&amp;","</f>
+        <f t="shared" ref="V20:V32" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O20:U20)&amp;","</f>
         <v xml:space="preserve">    3.83196430208642, 4.36032467052554, 4.79877351918793, 5.12629653673303, 7.08725879982336, 9.74577365763467, 10.0215788568391,</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="85"/>
+      <c r="B21" s="78"/>
       <c r="C21" s="30">
         <v>87.268396410214976</v>
       </c>
@@ -2056,13 +2056,13 @@
       <c r="J21" s="24"/>
       <c r="K21" s="24"/>
       <c r="L21" s="74" t="str">
-        <f t="shared" ref="L21:L27" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
+        <f t="shared" ref="L21:L27" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M21" s="83" t="s">
+      <c r="M21" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="85"/>
+      <c r="N21" s="78"/>
       <c r="O21" s="30">
         <v>2.610595868561878</v>
       </c>
@@ -2085,36 +2085,36 @@
         <v>4.1161081119796732</v>
       </c>
       <c r="V21" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    2.61059586856188, 2.32098052702246, 2.44262441526999, 2.28212554429868, 2.52313174140091, 3.76261004193711, 4.11610811197967,</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="85"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="78"/>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
       <c r="L22" s="74"/>
-      <c r="M22" s="83" t="s">
+      <c r="M22" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="84"/>
-      <c r="U22" s="85"/>
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="79"/>
+      <c r="R22" s="79"/>
+      <c r="S22" s="79"/>
+      <c r="T22" s="79"/>
+      <c r="U22" s="78"/>
       <c r="V22" s="74"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2148,7 +2148,7 @@
       <c r="J23" s="24"/>
       <c r="K23" s="24"/>
       <c r="L23" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    92.8344030500326, 91.6276501031568, 90.6873126312629, 88.3082552696756, 85.4291994865992, 68.0351400983128, 43.7765678965047,</v>
       </c>
       <c r="M23" s="28" t="s">
@@ -2179,7 +2179,7 @@
         <v>5.8871667869216564</v>
       </c>
       <c r="V23" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.73238091080979, 4.20096342452446, 3.80728801949415, 3.22471289436121, 3.52149367752585, 6.74400863714094, 5.88716678692166,</v>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       <c r="J24" s="24"/>
       <c r="K24" s="24"/>
       <c r="L24" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    92.5704084820554, 91.7777118862701, 90.8626103984622, 88.1999347172848, 86.1481154471343, 70.2700136242475, 45.7691453219754,</v>
       </c>
       <c r="M24" s="28" t="s">
@@ -2245,7 +2245,7 @@
         <v>4.6113240055125742</v>
       </c>
       <c r="V24" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.99175321800343, 3.8758943595963, 3.69040049210262, 3.15779253329341, 3.48255161572934, 5.89310384082912, 4.61132400551257,</v>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       <c r="J25" s="24"/>
       <c r="K25" s="24"/>
       <c r="L25" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    92.3295796845364, 91.7629456538786, 90.8734274982448, 88.69934964584, 86.3955943481394, 71.930170365072, 46.496036978427,</v>
       </c>
       <c r="M25" s="28" t="s">
@@ -2311,7 +2311,7 @@
         <v>5.1308639155298703</v>
       </c>
       <c r="V25" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.93680855637421, 3.92423982645902, 3.50601100349978, 3.1354282482648, 3.19891804474153, 4.80461477962954, 5.13086391552987,</v>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       <c r="J26" s="24"/>
       <c r="K26" s="24"/>
       <c r="L26" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    92.4863188787424, 92.3146749494195, 91.0729149813333, 89.1796017351206, 87.4639813817423, 74.6340733116706, 47.8503737326179,</v>
       </c>
       <c r="M26" s="28" t="s">
@@ -2377,7 +2377,7 @@
         <v>5.9411267054027839</v>
       </c>
       <c r="V26" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.54335705038537, 3.62767995604429, 3.2148388665628, 3.15148444918696, 3.08357573800914, 5.5553189785323, 5.94112670540278,</v>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
       <c r="L27" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
       <c r="M27" s="29" t="s">
@@ -2443,43 +2443,43 @@
         <v>6.1375770825509051</v>
       </c>
       <c r="V27" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.45837660705662, 3.62133151243551, 3.41882765616103, 3.25439791408069, 3.20212682277844, 5.23589217814922, 6.13757708255091,</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="84"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="81"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="74"/>
-      <c r="M28" s="83" t="s">
+      <c r="M28" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="84"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="86"/>
-      <c r="S28" s="86"/>
-      <c r="T28" s="86"/>
-      <c r="U28" s="87"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="80"/>
+      <c r="Q28" s="80"/>
+      <c r="R28" s="80"/>
+      <c r="S28" s="80"/>
+      <c r="T28" s="80"/>
+      <c r="U28" s="81"/>
       <c r="V28" s="74"/>
     </row>
     <row r="29" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83" t="s">
+      <c r="A29" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="85"/>
+      <c r="B29" s="78"/>
       <c r="C29" s="61">
         <v>92.603769819293618</v>
       </c>
@@ -2504,13 +2504,13 @@
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
       <c r="L29" s="74" t="str">
-        <f t="shared" ref="L29:L32" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
+        <f t="shared" ref="L29:L32" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M29" s="83" t="s">
+      <c r="M29" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="N29" s="85"/>
+      <c r="N29" s="78"/>
       <c r="O29" s="61">
         <v>3.708759274801273</v>
       </c>
@@ -2533,15 +2533,15 @@
         <v>6.3187793027043018</v>
       </c>
       <c r="V29" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="88" t="s">
+      <c r="A30" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="87"/>
+      <c r="B30" s="81"/>
       <c r="C30" s="64">
         <v>91.377634404932721</v>
       </c>
@@ -2566,13 +2566,13 @@
       <c r="J30" s="24"/>
       <c r="K30" s="24"/>
       <c r="L30" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M30" s="83" t="s">
+      <c r="M30" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="85"/>
+      <c r="N30" s="78"/>
       <c r="O30" s="64">
         <v>3.5684194304484111</v>
       </c>
@@ -2595,15 +2595,15 @@
         <v>2.9223071611371929</v>
       </c>
       <c r="V30" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="85"/>
+      <c r="B31" s="78"/>
       <c r="C31" s="64">
         <v>92.603715202692385</v>
       </c>
@@ -2628,13 +2628,13 @@
       <c r="J31" s="24"/>
       <c r="K31" s="24"/>
       <c r="L31" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M31" s="83" t="s">
+      <c r="M31" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="N31" s="85"/>
+      <c r="N31" s="78"/>
       <c r="O31" s="64">
         <v>4.0727132923350373</v>
       </c>
@@ -2657,15 +2657,15 @@
         <v>10.707618741543239</v>
       </c>
       <c r="V31" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="83" t="s">
+      <c r="A32" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="85"/>
+      <c r="B32" s="78"/>
       <c r="C32" s="67">
         <v>92.692685851985146</v>
       </c>
@@ -2690,13 +2690,13 @@
       <c r="J32" s="24"/>
       <c r="K32" s="24"/>
       <c r="L32" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M32" s="83" t="s">
+      <c r="M32" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="N32" s="85"/>
+      <c r="N32" s="78"/>
       <c r="O32" s="67">
         <v>4.3508377678439567</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>10.478269846537319</v>
       </c>
       <c r="V32" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    4.35083776784396, 5.14551979845971, 5.03194492579449, 5.48810922346629, 8.39637249074013, 11.2647747680684, 10.4782698465373,</v>
       </c>
     </row>
@@ -2861,6 +2861,34 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="M2:U2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="M18:U18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="M22:U22"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A32:B32"/>
@@ -2871,36 +2899,32 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="M22:U22"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="M18:U18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="M2:U2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:I4">
+    <cfRule type="colorScale" priority="107">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C6:I10 C3:I4">
     <cfRule type="colorScale" priority="19">
       <colorScale>
@@ -2967,92 +2991,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K15 C3:K4">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K5 C4:K4">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:I4">
-    <cfRule type="colorScale" priority="107">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J3:J15">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -3066,7 +3004,81 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:K15">
-    <cfRule type="colorScale" priority="119">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:K5 C4:K4">
+    <cfRule type="colorScale" priority="141">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="142">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="143">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="144">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="145">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="146">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:K15 C3:K4">
+    <cfRule type="colorScale" priority="153">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3078,19 +3090,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K15">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="155">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3185,38 +3185,38 @@
       <c r="V1" s="72"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="79"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="84"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="72"/>
-      <c r="M2" s="77" t="s">
+      <c r="M2" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="79"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="84"/>
       <c r="V2" s="72"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="15">
         <v>93.101364775358491</v>
       </c>
@@ -3250,10 +3250,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M3" s="77" t="s">
+      <c r="M3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="79"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="15">
         <v>3.4649270444699574</v>
       </c>
@@ -3281,10 +3281,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="22">
         <v>87.593900000000005</v>
       </c>
@@ -3315,13 +3315,13 @@
         <v>81.468931946607086</v>
       </c>
       <c r="L4" s="72" t="str">
-        <f t="shared" ref="L4:L10" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="77" t="s">
+      <c r="M4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="79"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="51">
         <v>2.4529187882918819</v>
       </c>
@@ -3344,36 +3344,36 @@
         <v>3.7419646549723868</v>
       </c>
       <c r="V4" s="72" t="str">
-        <f t="shared" ref="V4:V10" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O4:U4)&amp;","</f>
+        <f t="shared" ref="V4:V10" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O4:U4)&amp;","</f>
         <v xml:space="preserve">    2.45291878829188, 2.16276566139488, 2.29733988047472, 2.13416531965459, 2.38348787528267, 3.78798604641006, 3.74196465497239,</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="84"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="72"/>
-      <c r="M5" s="77" t="s">
+      <c r="M5" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="79"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="87"/>
+      <c r="U5" s="84"/>
       <c r="V5" s="72"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3413,7 +3413,7 @@
         <v>83.402759395265804</v>
       </c>
       <c r="L6" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:I6)&amp;","</f>
         <v xml:space="preserve">    92.2792527040315, 92.1533923303835, 91.8180924287119, 89.0137717454303, 85.8583205737074, 67.2664498251138, 47.5020948854806,</v>
       </c>
       <c r="M6" s="21" t="s">
@@ -3444,7 +3444,7 @@
         <v>4.8064970172268771</v>
       </c>
       <c r="V6" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.28570786908175, 3.10107000820236, 3.17538510931435, 3.03420640942368, 2.97627372633855, 4.93985455382171, 4.80649701722688,</v>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>83.424706096073507</v>
       </c>
       <c r="L7" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:I7)&amp;","</f>
         <v xml:space="preserve">    91.7060038004942, 91.5889872173058, 91.2920700006055, 88.92133726647, 86.9076750952286, 70.6025888343901, 47.9732321790558,</v>
       </c>
       <c r="M7" s="21" t="s">
@@ -3516,7 +3516,7 @@
         <v>3.8082729656882011</v>
       </c>
       <c r="V7" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    3.0791601252178, 3.05157675530851, 2.99056701375987, 2.79437545290244, 2.94178873640284, 4.64029809794241, 3.8082729656882,</v>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
         <v>83.28504759268391</v>
       </c>
       <c r="L8" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C8:I8)&amp;","</f>
         <v xml:space="preserve">    90.5447394296952, 91.3451327433629, 90.9960668633235, 88.7487204329911, 87.2951755638024, 72.2465476921657, 47.8496094256871,</v>
       </c>
       <c r="M8" s="21" t="s">
@@ -3588,7 +3588,7 @@
         <v>4.3986399547690587</v>
       </c>
       <c r="V8" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    2.94260400814314, 2.86228532617839, 2.75503888995263, 2.67104901051394, 2.5041283309246, 4.12727076079131, 4.39863995476906,</v>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
         <v>83.836633967421861</v>
       </c>
       <c r="L9" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    90.8662791200616, 90.7611196175284, 90.2559653053515, 89.6691061341361, 88.4720138870867, 78.715231100615, 51.17069351811,</v>
       </c>
       <c r="M9" s="21" t="s">
@@ -3660,7 +3660,7 @@
         <v>6.0857090074716371</v>
       </c>
       <c r="V9" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    2.87353602218358, 2.83371043928934, 2.85547832524272, 2.63642180310144, 2.5235875259162, 3.65662359267695, 6.08570900747164,</v>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
         <v>83.373629313402375</v>
       </c>
       <c r="L10" s="72" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:I10)&amp;","</f>
         <v xml:space="preserve">    90.2399213372665, 89.8820174338302, 90.283185840708, 89.1485451142888, 87.8440124914575, 77.6000484433256, 53.3092529635493,</v>
       </c>
       <c r="M10" s="4" t="s">
@@ -3732,43 +3732,43 @@
         <v>6.2823918133732528</v>
       </c>
       <c r="V10" s="72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    2.79668973883751, 2.81626030048225, 2.61122881188715, 2.6757318856272, 2.89093551272523, 4.7145823833882, 6.28239181337325,</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="81"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="86"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="72"/>
-      <c r="M11" s="77" t="s">
+      <c r="M11" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="78"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="80"/>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80"/>
-      <c r="U11" s="81"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="86"/>
       <c r="V11" s="72"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -3799,13 +3799,13 @@
         <v>81.635477022580943</v>
       </c>
       <c r="L12" s="72" t="str">
-        <f t="shared" ref="L12:L15" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M12" s="77" t="s">
+      <c r="M12" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="N12" s="79"/>
+      <c r="N12" s="84"/>
       <c r="O12" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -3828,15 +3828,15 @@
         <v>5.203571843512913</v>
       </c>
       <c r="V12" s="72" t="str">
-        <f t="shared" ref="V12:V15" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O12:U12)&amp;","</f>
+        <f t="shared" ref="V12:V15" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O12:U12)&amp;","</f>
         <v xml:space="preserve">    3.39919218235549, 3.656148978379, 3.43161793888068, 3.36107812276178, 5.27738358730928, 8.20271301965104, 5.20357184351291,</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="81"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -3867,13 +3867,13 @@
         <v>82.625440098962798</v>
       </c>
       <c r="L13" s="72" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C13:I13)&amp;","</f>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M13" s="77" t="s">
+      <c r="M13" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="79"/>
+      <c r="N13" s="84"/>
       <c r="O13" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -3896,15 +3896,15 @@
         <v>2.488810891584841</v>
       </c>
       <c r="V13" s="72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.19031227155556, 2.88280360646228, 2.58847407711463, 2.62134504708773, 3.20356998968766, 4.75671211275067, 2.48881089158484,</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="79"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -3935,13 +3935,13 @@
         <v>81.55872152873296</v>
       </c>
       <c r="L14" s="72" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M14" s="77" t="s">
+      <c r="M14" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="N14" s="79"/>
+      <c r="N14" s="84"/>
       <c r="O14" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -3964,15 +3964,15 @@
         <v>9.2355901481835172</v>
       </c>
       <c r="V14" s="72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.72078192123604, 4.04671527762167, 4.023576362777, 4.47676332123312, 7.20190165275039, 10.0466843686008, 9.23559014818352,</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="79"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="58">
         <v>93.174110502686005</v>
       </c>
@@ -4003,13 +4003,13 @@
         <v>80.686930106085114</v>
       </c>
       <c r="L15" s="72" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:I15)&amp;","</f>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M15" s="77" t="s">
+      <c r="M15" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="N15" s="79"/>
+      <c r="N15" s="84"/>
       <c r="O15" s="58">
         <v>3.8766021792735019</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>9.200486032966916</v>
       </c>
       <c r="V15" s="72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.8766021792735, 4.81264114062281, 4.6512210016048, 5.24160663557633, 8.07695886022353, 10.6573633075615, 9.20048603296692,</v>
       </c>
     </row>
@@ -4121,38 +4121,38 @@
       <c r="V17" s="74"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="84"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="85"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="78"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="74"/>
-      <c r="M18" s="83" t="s">
+      <c r="M18" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="84"/>
-      <c r="O18" s="84"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="85"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="79"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="78"/>
       <c r="V18" s="74"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="85"/>
+      <c r="B19" s="78"/>
       <c r="C19" s="25">
         <v>92.567111769713335</v>
       </c>
@@ -4180,10 +4180,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M19" s="83" t="s">
+      <c r="M19" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="N19" s="85"/>
+      <c r="N19" s="78"/>
       <c r="O19" s="27">
         <v>3.88093621561358</v>
       </c>
@@ -4211,10 +4211,10 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="85"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="25">
         <v>92.866950218042462</v>
       </c>
@@ -4242,10 +4242,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M20" s="83" t="s">
+      <c r="M20" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="N20" s="85"/>
+      <c r="N20" s="78"/>
       <c r="O20" s="25">
         <v>3.8319643020864191</v>
       </c>
@@ -4268,15 +4268,15 @@
         <v>10.021578856839133</v>
       </c>
       <c r="V20" s="74" t="str">
-        <f t="shared" ref="V20:V32" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O20:U20)&amp;","</f>
+        <f t="shared" ref="V20:V32" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O20:U20)&amp;","</f>
         <v xml:space="preserve">    3.83196430208642, 4.36032467052554, 4.79877351918793, 5.12629653673303, 7.08725879982336, 9.74577365763467, 10.0215788568391,</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="85"/>
+      <c r="B21" s="78"/>
       <c r="C21" s="30">
         <v>87.268396410214976</v>
       </c>
@@ -4301,13 +4301,13 @@
       <c r="J21" s="24"/>
       <c r="K21" s="24"/>
       <c r="L21" s="74" t="str">
-        <f t="shared" ref="L21:L27" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
+        <f t="shared" ref="L21:L27" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M21" s="83" t="s">
+      <c r="M21" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="85"/>
+      <c r="N21" s="78"/>
       <c r="O21" s="30">
         <v>2.610595868561878</v>
       </c>
@@ -4330,36 +4330,36 @@
         <v>4.1161081119796732</v>
       </c>
       <c r="V21" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    2.61059586856188, 2.32098052702246, 2.44262441526999, 2.28212554429868, 2.52313174140091, 3.76261004193711, 4.11610811197967,</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="85"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="78"/>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
       <c r="L22" s="74"/>
-      <c r="M22" s="83" t="s">
+      <c r="M22" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="84"/>
-      <c r="U22" s="85"/>
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="79"/>
+      <c r="R22" s="79"/>
+      <c r="S22" s="79"/>
+      <c r="T22" s="79"/>
+      <c r="U22" s="78"/>
       <c r="V22" s="74"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -4393,7 +4393,7 @@
       <c r="J23" s="24"/>
       <c r="K23" s="24"/>
       <c r="L23" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    91.8318867067327, 91.6294810205574, 91.4616478300887, 88.6679648469171, 85.3461070481928, 66.8029042059518, 45.032918543413,</v>
       </c>
       <c r="M23" s="28" t="s">
@@ -4424,7 +4424,7 @@
         <v>5.4498307804832438</v>
       </c>
       <c r="V23" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.58612365952748, 3.4347135002308, 3.41711013492947, 3.1908353983567, 3.11773789077584, 5.10579247875884, 5.44983078048324,</v>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       <c r="J24" s="24"/>
       <c r="K24" s="24"/>
       <c r="L24" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    91.3141346295792, 91.267939380912, 90.9330562612071, 88.5719482020041, 86.6388103536492, 70.2280494083782, 45.9671912593586,</v>
       </c>
       <c r="M24" s="28" t="s">
@@ -4490,7 +4490,7 @@
         <v>4.2370718967403684</v>
       </c>
       <c r="V24" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.2670247855157, 3.27872749040298, 3.19270323043257, 2.9467329042029, 2.99268068356301, 4.69537499674566, 4.23707189674037,</v>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       <c r="J25" s="24"/>
       <c r="K25" s="24"/>
       <c r="L25" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    90.1269331704954, 90.8515554720174, 90.716004051495, 88.4456944117682, 86.9937464129196, 71.9296588807976, 46.3212131559758,</v>
       </c>
       <c r="M25" s="28" t="s">
@@ -4556,7 +4556,7 @@
         <v>4.5689995150432843</v>
       </c>
       <c r="V25" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.17895492709927, 3.16076433767299, 2.89307513160949, 2.71316625467466, 2.47740041726617, 4.18464907356885, 4.56899951504328,</v>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       <c r="J26" s="24"/>
       <c r="K26" s="24"/>
       <c r="L26" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    90.3975341072725, 90.2757042351886, 89.859122752766, 89.3809050856424, 88.100060763176, 78.3277038434056, 49.9645468383793,</v>
       </c>
       <c r="M26" s="28" t="s">
@@ -4622,7 +4622,7 @@
         <v>6.4302409812546122</v>
       </c>
       <c r="V26" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.18119667872183, 3.14808098645014, 3.02571965711434, 2.6978750836679, 2.69811624795075, 3.84186555361098, 6.43024098125461,</v>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
       <c r="L27" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    89.7854537644522, 89.3697777314809, 89.9680318532672, 88.8508565927458, 87.5704893420754, 77.3895989110905, 52.1142760050885,</v>
       </c>
       <c r="M27" s="29" t="s">
@@ -4688,43 +4688,43 @@
         <v>6.480299208283995</v>
       </c>
       <c r="V27" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    2.97876954790739, 3.07941231663607, 2.75871242127261, 2.78737375363297, 2.94815996763878, 4.78257839595089, 6.48029920828399,</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="84"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="81"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="74"/>
-      <c r="M28" s="83" t="s">
+      <c r="M28" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="84"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="86"/>
-      <c r="S28" s="86"/>
-      <c r="T28" s="86"/>
-      <c r="U28" s="87"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="80"/>
+      <c r="Q28" s="80"/>
+      <c r="R28" s="80"/>
+      <c r="S28" s="80"/>
+      <c r="T28" s="80"/>
+      <c r="U28" s="81"/>
       <c r="V28" s="74"/>
     </row>
     <row r="29" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83" t="s">
+      <c r="A29" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="85"/>
+      <c r="B29" s="78"/>
       <c r="C29" s="61">
         <v>92.603769819293618</v>
       </c>
@@ -4749,13 +4749,13 @@
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
       <c r="L29" s="74" t="str">
-        <f t="shared" ref="L29:L32" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
+        <f t="shared" ref="L29:L32" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M29" s="83" t="s">
+      <c r="M29" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="N29" s="85"/>
+      <c r="N29" s="78"/>
       <c r="O29" s="61">
         <v>3.708759274801273</v>
       </c>
@@ -4778,15 +4778,15 @@
         <v>6.3187793027043018</v>
       </c>
       <c r="V29" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="88" t="s">
+      <c r="A30" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="87"/>
+      <c r="B30" s="81"/>
       <c r="C30" s="64">
         <v>91.377634404932721</v>
       </c>
@@ -4811,13 +4811,13 @@
       <c r="J30" s="24"/>
       <c r="K30" s="24"/>
       <c r="L30" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M30" s="83" t="s">
+      <c r="M30" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="85"/>
+      <c r="N30" s="78"/>
       <c r="O30" s="64">
         <v>3.5684194304484111</v>
       </c>
@@ -4840,15 +4840,15 @@
         <v>2.9223071611371929</v>
       </c>
       <c r="V30" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="85"/>
+      <c r="B31" s="78"/>
       <c r="C31" s="64">
         <v>92.603715202692385</v>
       </c>
@@ -4873,13 +4873,13 @@
       <c r="J31" s="24"/>
       <c r="K31" s="24"/>
       <c r="L31" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M31" s="83" t="s">
+      <c r="M31" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="N31" s="85"/>
+      <c r="N31" s="78"/>
       <c r="O31" s="64">
         <v>4.0727132923350373</v>
       </c>
@@ -4902,15 +4902,15 @@
         <v>10.707618741543239</v>
       </c>
       <c r="V31" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="83" t="s">
+      <c r="A32" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="85"/>
+      <c r="B32" s="78"/>
       <c r="C32" s="67">
         <v>92.692685851985146</v>
       </c>
@@ -4935,13 +4935,13 @@
       <c r="J32" s="24"/>
       <c r="K32" s="24"/>
       <c r="L32" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M32" s="83" t="s">
+      <c r="M32" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="N32" s="85"/>
+      <c r="N32" s="78"/>
       <c r="O32" s="67">
         <v>4.3508377678439567</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>10.478269846537319</v>
       </c>
       <c r="V32" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    4.35083776784396, 5.14551979845971, 5.03194492579449, 5.48810922346629, 8.39637249074013, 11.2647747680684, 10.4782698465373,</v>
       </c>
     </row>
@@ -5106,28 +5106,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="M28:U28"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="M5:U5"/>
     <mergeCell ref="A2:I2"/>
@@ -5144,10 +5122,56 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M28:U28"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M11:U11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:I4">
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C6:I10 C3:I4">
-    <cfRule type="colorScale" priority="84">
+    <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5159,7 +5183,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I14">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5169,7 +5193,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5179,7 +5203,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5189,7 +5213,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5201,7 +5225,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I15">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5212,8 +5236,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K15 C3:K4">
-    <cfRule type="colorScale" priority="43">
+  <conditionalFormatting sqref="J3:J15">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23:J28">
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:K15">
+    <cfRule type="colorScale" priority="156">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5225,7 +5273,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C4:K4">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="159">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5235,7 +5283,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="160">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5245,7 +5293,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="161">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5255,7 +5303,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5265,7 +5313,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="163">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5275,7 +5323,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5286,8 +5334,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J23:J28">
-    <cfRule type="colorScale" priority="98">
+  <conditionalFormatting sqref="C3:K4 J5:K15">
+    <cfRule type="colorScale" priority="171">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5299,7 +5347,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:K28">
-    <cfRule type="colorScale" priority="100">
+    <cfRule type="colorScale" priority="175">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5309,7 +5357,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="101">
+    <cfRule type="colorScale" priority="176">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K15">
+    <cfRule type="colorScale" priority="177">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5321,67 +5381,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:K28">
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:I4">
-    <cfRule type="colorScale" priority="124">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J15">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:K15">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K15">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results_(stress_test)_PCCxSigmoid-PLI-/summary_PCC_PLI_20250413.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/summary_PCC_PLI_20250413.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9518283-9AAF-4904-9A14-23B8AC7D6220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B590DEFE-C747-4F57-8109-69AD07AA8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nm_basis_F, nm_modifier_F" sheetId="8" r:id="rId1"/>
@@ -3004,7 +3004,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:K15">
-    <cfRule type="colorScale" priority="140">
+    <cfRule type="colorScale" priority="209">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3016,7 +3016,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C4:K4">
-    <cfRule type="colorScale" priority="141">
+    <cfRule type="colorScale" priority="210">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3026,7 +3026,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="142">
+    <cfRule type="colorScale" priority="211">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3036,7 +3036,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="143">
+    <cfRule type="colorScale" priority="212">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3046,7 +3046,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="144">
+    <cfRule type="colorScale" priority="213">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3056,7 +3056,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="145">
+    <cfRule type="colorScale" priority="214">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3066,7 +3066,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="146">
+    <cfRule type="colorScale" priority="215">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3078,7 +3078,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K15 C3:K4">
-    <cfRule type="colorScale" priority="153">
+    <cfRule type="colorScale" priority="222">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3090,7 +3090,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K15">
-    <cfRule type="colorScale" priority="155">
+    <cfRule type="colorScale" priority="224">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5147,7 +5147,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5159,7 +5159,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:I4">
-    <cfRule type="colorScale" priority="127">
+    <cfRule type="colorScale" priority="130">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5171,7 +5171,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:I10 C3:I4">
-    <cfRule type="colorScale" priority="87">
+    <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5183,7 +5183,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I14">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5193,7 +5193,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5203,7 +5203,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5213,7 +5213,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5225,7 +5225,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I15">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5237,7 +5237,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J15">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5249,7 +5249,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J28">
-    <cfRule type="colorScale" priority="101">
+    <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5261,7 +5261,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:K15">
-    <cfRule type="colorScale" priority="156">
+    <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5273,7 +5273,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C4:K4">
-    <cfRule type="colorScale" priority="159">
+    <cfRule type="colorScale" priority="187">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5283,7 +5283,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="160">
+    <cfRule type="colorScale" priority="188">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5293,7 +5293,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="161">
+    <cfRule type="colorScale" priority="189">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5303,7 +5303,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="162">
+    <cfRule type="colorScale" priority="190">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5313,7 +5313,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="163">
+    <cfRule type="colorScale" priority="191">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5323,7 +5323,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="164">
+    <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5335,7 +5335,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:K4 J5:K15">
-    <cfRule type="colorScale" priority="171">
+    <cfRule type="colorScale" priority="199">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5347,7 +5347,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:K28">
-    <cfRule type="colorScale" priority="175">
+    <cfRule type="colorScale" priority="203">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5357,7 +5357,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="176">
+    <cfRule type="colorScale" priority="204">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5369,7 +5369,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K15">
-    <cfRule type="colorScale" priority="177">
+    <cfRule type="colorScale" priority="205">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5381,7 +5381,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:K28">
-    <cfRule type="colorScale" priority="180">
+    <cfRule type="colorScale" priority="208">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results_(stress_test)_PCCxSigmoid-PLI-/summary_PCC_PLI_20250413.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/summary_PCC_PLI_20250413.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B590DEFE-C747-4F57-8109-69AD07AA8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -547,15 +547,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -565,27 +583,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -940,38 +940,38 @@
       <c r="V1" s="72"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="84"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="79"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="72"/>
-      <c r="M2" s="83" t="s">
+      <c r="M2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="87"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="87"/>
-      <c r="U2" s="84"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="79"/>
       <c r="V2" s="72"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="84"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="15">
         <v>93.101364775358491</v>
       </c>
@@ -1005,10 +1005,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M3" s="83" t="s">
+      <c r="M3" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="84"/>
+      <c r="N3" s="79"/>
       <c r="O3" s="15">
         <v>3.4649270444699574</v>
       </c>
@@ -1036,10 +1036,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="22">
         <v>87.593900000000005</v>
       </c>
@@ -1073,10 +1073,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="83" t="s">
+      <c r="M4" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="84"/>
+      <c r="N4" s="79"/>
       <c r="O4" s="51">
         <v>2.4529187882918819</v>
       </c>
@@ -1104,31 +1104,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="84"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="79"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="72"/>
-      <c r="M5" s="83" t="s">
+      <c r="M5" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="84"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="79"/>
       <c r="V5" s="72"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1492,38 +1492,38 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="86"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="81"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="72"/>
-      <c r="M11" s="83" t="s">
+      <c r="M11" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="87"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="86"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="81"/>
       <c r="V11" s="72"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="84"/>
+      <c r="B12" s="79"/>
       <c r="C12" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -1557,10 +1557,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M12" s="83" t="s">
+      <c r="M12" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="N12" s="84"/>
+      <c r="N12" s="79"/>
       <c r="O12" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -1588,10 +1588,10 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="86"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -1625,10 +1625,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C13:I13)&amp;","</f>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M13" s="83" t="s">
+      <c r="M13" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="84"/>
+      <c r="N13" s="79"/>
       <c r="O13" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -1656,10 +1656,10 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="84"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -1693,10 +1693,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M14" s="83" t="s">
+      <c r="M14" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="N14" s="84"/>
+      <c r="N14" s="79"/>
       <c r="O14" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -1724,10 +1724,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="84"/>
+      <c r="B15" s="79"/>
       <c r="C15" s="58">
         <v>93.174110502686005</v>
       </c>
@@ -1761,10 +1761,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:I15)&amp;","</f>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M15" s="83" t="s">
+      <c r="M15" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="N15" s="84"/>
+      <c r="N15" s="79"/>
       <c r="O15" s="58">
         <v>3.8766021792735019</v>
       </c>
@@ -1876,38 +1876,38 @@
       <c r="V17" s="74"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="78"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="74"/>
-      <c r="M18" s="77" t="s">
+      <c r="M18" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
-      <c r="Q18" s="79"/>
-      <c r="R18" s="79"/>
-      <c r="S18" s="79"/>
-      <c r="T18" s="79"/>
-      <c r="U18" s="78"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="84"/>
+      <c r="U18" s="85"/>
       <c r="V18" s="74"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="78"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="25">
         <v>92.567111769713335</v>
       </c>
@@ -1935,10 +1935,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M19" s="77" t="s">
+      <c r="M19" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="N19" s="78"/>
+      <c r="N19" s="85"/>
       <c r="O19" s="27">
         <v>3.88093621561358</v>
       </c>
@@ -1966,10 +1966,10 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="78"/>
+      <c r="B20" s="85"/>
       <c r="C20" s="25">
         <v>92.866950218042462</v>
       </c>
@@ -1997,10 +1997,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M20" s="77" t="s">
+      <c r="M20" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="N20" s="78"/>
+      <c r="N20" s="85"/>
       <c r="O20" s="25">
         <v>3.8319643020864191</v>
       </c>
@@ -2028,10 +2028,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="78"/>
+      <c r="B21" s="85"/>
       <c r="C21" s="30">
         <v>87.268396410214976</v>
       </c>
@@ -2059,10 +2059,10 @@
         <f t="shared" ref="L21:L27" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M21" s="77" t="s">
+      <c r="M21" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="78"/>
+      <c r="N21" s="85"/>
       <c r="O21" s="30">
         <v>2.610595868561878</v>
       </c>
@@ -2090,31 +2090,31 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="78"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85"/>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
       <c r="L22" s="74"/>
-      <c r="M22" s="77" t="s">
+      <c r="M22" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="79"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="79"/>
-      <c r="Q22" s="79"/>
-      <c r="R22" s="79"/>
-      <c r="S22" s="79"/>
-      <c r="T22" s="79"/>
-      <c r="U22" s="78"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="85"/>
       <c r="V22" s="74"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2448,38 +2448,38 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="81"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="87"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="74"/>
-      <c r="M28" s="77" t="s">
+      <c r="M28" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="79"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="80"/>
-      <c r="Q28" s="80"/>
-      <c r="R28" s="80"/>
-      <c r="S28" s="80"/>
-      <c r="T28" s="80"/>
-      <c r="U28" s="81"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="87"/>
       <c r="V28" s="74"/>
     </row>
     <row r="29" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="77" t="s">
+      <c r="A29" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="78"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="61">
         <v>92.603769819293618</v>
       </c>
@@ -2507,10 +2507,10 @@
         <f t="shared" ref="L29:L32" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M29" s="77" t="s">
+      <c r="M29" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="N29" s="78"/>
+      <c r="N29" s="85"/>
       <c r="O29" s="61">
         <v>3.708759274801273</v>
       </c>
@@ -2538,10 +2538,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="81"/>
+      <c r="B30" s="87"/>
       <c r="C30" s="64">
         <v>91.377634404932721</v>
       </c>
@@ -2569,10 +2569,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M30" s="77" t="s">
+      <c r="M30" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="78"/>
+      <c r="N30" s="85"/>
       <c r="O30" s="64">
         <v>3.5684194304484111</v>
       </c>
@@ -2600,10 +2600,10 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="77" t="s">
+      <c r="A31" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="78"/>
+      <c r="B31" s="85"/>
       <c r="C31" s="64">
         <v>92.603715202692385</v>
       </c>
@@ -2631,10 +2631,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M31" s="77" t="s">
+      <c r="M31" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="N31" s="78"/>
+      <c r="N31" s="85"/>
       <c r="O31" s="64">
         <v>4.0727132923350373</v>
       </c>
@@ -2662,10 +2662,10 @@
       </c>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="78"/>
+      <c r="B32" s="85"/>
       <c r="C32" s="67">
         <v>92.692685851985146</v>
       </c>
@@ -2693,10 +2693,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M32" s="77" t="s">
+      <c r="M32" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="N32" s="78"/>
+      <c r="N32" s="85"/>
       <c r="O32" s="67">
         <v>4.3508377678439567</v>
       </c>
@@ -2861,36 +2861,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="M2:U2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="M18:U18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="M22:U22"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="M31:N31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="M32:N32"/>
     <mergeCell ref="A28:I28"/>
@@ -2899,6 +2869,36 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="M22:U22"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="M18:U18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="M2:U2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
@@ -3185,38 +3185,38 @@
       <c r="V1" s="72"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="84"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="79"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="72"/>
-      <c r="M2" s="83" t="s">
+      <c r="M2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="87"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="87"/>
-      <c r="U2" s="84"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="79"/>
       <c r="V2" s="72"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="84"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="15">
         <v>93.101364775358491</v>
       </c>
@@ -3250,10 +3250,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M3" s="83" t="s">
+      <c r="M3" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="84"/>
+      <c r="N3" s="79"/>
       <c r="O3" s="15">
         <v>3.4649270444699574</v>
       </c>
@@ -3281,10 +3281,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="22">
         <v>87.593900000000005</v>
       </c>
@@ -3318,10 +3318,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="83" t="s">
+      <c r="M4" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="84"/>
+      <c r="N4" s="79"/>
       <c r="O4" s="51">
         <v>2.4529187882918819</v>
       </c>
@@ -3349,31 +3349,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="84"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="79"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="72"/>
-      <c r="M5" s="83" t="s">
+      <c r="M5" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="84"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="79"/>
       <c r="V5" s="72"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3737,38 +3737,38 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="86"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="81"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="72"/>
-      <c r="M11" s="83" t="s">
+      <c r="M11" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="87"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="86"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="81"/>
       <c r="V11" s="72"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="84"/>
+      <c r="B12" s="79"/>
       <c r="C12" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -3802,10 +3802,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M12" s="83" t="s">
+      <c r="M12" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="N12" s="84"/>
+      <c r="N12" s="79"/>
       <c r="O12" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -3833,10 +3833,10 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="86"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -3870,10 +3870,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C13:I13)&amp;","</f>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M13" s="83" t="s">
+      <c r="M13" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="84"/>
+      <c r="N13" s="79"/>
       <c r="O13" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -3901,10 +3901,10 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="84"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -3938,10 +3938,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M14" s="83" t="s">
+      <c r="M14" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="N14" s="84"/>
+      <c r="N14" s="79"/>
       <c r="O14" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -3969,10 +3969,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="84"/>
+      <c r="B15" s="79"/>
       <c r="C15" s="58">
         <v>93.174110502686005</v>
       </c>
@@ -4006,10 +4006,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:I15)&amp;","</f>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M15" s="83" t="s">
+      <c r="M15" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="N15" s="84"/>
+      <c r="N15" s="79"/>
       <c r="O15" s="58">
         <v>3.8766021792735019</v>
       </c>
@@ -4121,38 +4121,38 @@
       <c r="V17" s="74"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="78"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="74"/>
-      <c r="M18" s="77" t="s">
+      <c r="M18" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
-      <c r="Q18" s="79"/>
-      <c r="R18" s="79"/>
-      <c r="S18" s="79"/>
-      <c r="T18" s="79"/>
-      <c r="U18" s="78"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="84"/>
+      <c r="U18" s="85"/>
       <c r="V18" s="74"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="78"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="25">
         <v>92.567111769713335</v>
       </c>
@@ -4180,10 +4180,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M19" s="77" t="s">
+      <c r="M19" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="N19" s="78"/>
+      <c r="N19" s="85"/>
       <c r="O19" s="27">
         <v>3.88093621561358</v>
       </c>
@@ -4211,10 +4211,10 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="78"/>
+      <c r="B20" s="85"/>
       <c r="C20" s="25">
         <v>92.866950218042462</v>
       </c>
@@ -4242,10 +4242,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M20" s="77" t="s">
+      <c r="M20" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="N20" s="78"/>
+      <c r="N20" s="85"/>
       <c r="O20" s="25">
         <v>3.8319643020864191</v>
       </c>
@@ -4273,10 +4273,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="78"/>
+      <c r="B21" s="85"/>
       <c r="C21" s="30">
         <v>87.268396410214976</v>
       </c>
@@ -4304,10 +4304,10 @@
         <f t="shared" ref="L21:L27" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M21" s="77" t="s">
+      <c r="M21" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="78"/>
+      <c r="N21" s="85"/>
       <c r="O21" s="30">
         <v>2.610595868561878</v>
       </c>
@@ -4335,31 +4335,31 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="78"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85"/>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
       <c r="L22" s="74"/>
-      <c r="M22" s="77" t="s">
+      <c r="M22" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="79"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="79"/>
-      <c r="Q22" s="79"/>
-      <c r="R22" s="79"/>
-      <c r="S22" s="79"/>
-      <c r="T22" s="79"/>
-      <c r="U22" s="78"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="85"/>
       <c r="V22" s="74"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -4693,38 +4693,38 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="81"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="87"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="74"/>
-      <c r="M28" s="77" t="s">
+      <c r="M28" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="79"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="80"/>
-      <c r="Q28" s="80"/>
-      <c r="R28" s="80"/>
-      <c r="S28" s="80"/>
-      <c r="T28" s="80"/>
-      <c r="U28" s="81"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="87"/>
       <c r="V28" s="74"/>
     </row>
     <row r="29" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="77" t="s">
+      <c r="A29" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="78"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="61">
         <v>92.603769819293618</v>
       </c>
@@ -4752,10 +4752,10 @@
         <f t="shared" ref="L29:L32" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M29" s="77" t="s">
+      <c r="M29" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="N29" s="78"/>
+      <c r="N29" s="85"/>
       <c r="O29" s="61">
         <v>3.708759274801273</v>
       </c>
@@ -4783,10 +4783,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="81"/>
+      <c r="B30" s="87"/>
       <c r="C30" s="64">
         <v>91.377634404932721</v>
       </c>
@@ -4814,10 +4814,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M30" s="77" t="s">
+      <c r="M30" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="78"/>
+      <c r="N30" s="85"/>
       <c r="O30" s="64">
         <v>3.5684194304484111</v>
       </c>
@@ -4845,10 +4845,10 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="77" t="s">
+      <c r="A31" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="78"/>
+      <c r="B31" s="85"/>
       <c r="C31" s="64">
         <v>92.603715202692385</v>
       </c>
@@ -4876,10 +4876,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M31" s="77" t="s">
+      <c r="M31" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="N31" s="78"/>
+      <c r="N31" s="85"/>
       <c r="O31" s="64">
         <v>4.0727132923350373</v>
       </c>
@@ -4907,10 +4907,10 @@
       </c>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="78"/>
+      <c r="B32" s="85"/>
       <c r="C32" s="67">
         <v>92.692685851985146</v>
       </c>
@@ -4938,10 +4938,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M32" s="77" t="s">
+      <c r="M32" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="N32" s="78"/>
+      <c r="N32" s="85"/>
       <c r="O32" s="67">
         <v>4.3508377678439567</v>
       </c>
@@ -5106,6 +5106,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M28:U28"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="M5:U5"/>
     <mergeCell ref="A2:I2"/>
@@ -5122,28 +5144,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="M28:U28"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M11:U11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:I4 C6:I10 C12:I15">
@@ -5226,6 +5226,18 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I15">
     <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:K4 J5:K15">
+    <cfRule type="colorScale" priority="199">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5334,18 +5346,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:K4 J5:K15">
-    <cfRule type="colorScale" priority="199">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J23:K28">
     <cfRule type="colorScale" priority="203">
       <colorScale>
